--- a/Assets/Map/Stage.xlsx
+++ b/Assets/Map/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GE2A18\就職対策\就職作品関連\WizardTactics\Assets\Map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5E93A-A408-4985-B369-5648FBEC44A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FA6C55-309C-47EB-8787-C3F935DBEC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5F185F9-1631-48D0-AA58-F3F29CA46A5A}"/>
+    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{B5F185F9-1631-48D0-AA58-F3F29CA46A5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -923,114 +923,114 @@
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
